--- a/data_input/05_plan_lock.xlsx
+++ b/data_input/05_plan_lock.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="pre_plan_lock" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pre_plan_lock" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data_input/05_plan_lock.xlsx
+++ b/data_input/05_plan_lock.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -452,6 +452,16 @@
     <col width="17" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -590,6 +600,56 @@
           <t>opex_pct</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>guests</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>gift</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>gift_fixed</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>cost_ads</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>cost_kol</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>cost_posm</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>cost_other</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>backfill</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -699,6 +759,36 @@
       <c r="AA2" t="n">
         <v>0.092</v>
       </c>
+      <c r="AB2" t="n">
+        <v>1091</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>26080634</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>43416000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -803,6 +893,36 @@
       <c r="AA3" t="n">
         <v>0.08699999999999999</v>
       </c>
+      <c r="AB3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1654392</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>223918</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -907,6 +1027,36 @@
       <c r="AA4" t="n">
         <v>0.08699999999999999</v>
       </c>
+      <c r="AB4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1730123</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4122647</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1015,6 +1165,36 @@
       </c>
       <c r="AA5" t="n">
         <v>0.08699999999999999</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4783</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>134595390</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12003864</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/05_plan_lock.xlsx
+++ b/data_input/05_plan_lock.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK5"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1061,7 +1061,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>ALL-2026-10-LOYALTY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1071,37 +1071,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KHOA_MUON</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
+          <t>BAT_DAU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Set Lunch 199K (salad + main)</t>
+          <t>NOIRE Loyalty (toàn hệ thống) — duy trì giảm 10% thành viên</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET|NCB_MET|NCB_SKC|NDC_NTMK|NDC_BKL|NJFB_CRE|NJFB_SSV</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1116,85 +1111,1284 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TC_DAYPART</t>
+          <t>TC_FREQ</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>CHAY_THU</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2321</v>
+        <v>3336</v>
       </c>
       <c r="O5" t="n">
-        <v>3346</v>
+        <v>34180</v>
       </c>
       <c r="P5" t="n">
-        <v>0.69375137652204</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="R5" t="n">
-        <v>272364959</v>
+        <v>65088526</v>
       </c>
       <c r="S5" t="n">
-        <v>451051023</v>
+        <v>1651946800</v>
       </c>
       <c r="T5" t="n">
-        <v>97069954</v>
+        <v>5294546</v>
       </c>
       <c r="U5" t="n">
-        <v>56241972</v>
+        <v>3176728</v>
       </c>
       <c r="V5" t="n">
-        <v>5.708699761487024</v>
+        <v>0.05422917874905554</v>
       </c>
       <c r="W5" t="n">
-        <v>17003864</v>
+        <v>97632790</v>
       </c>
       <c r="X5" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>5171.850064627316</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0.33</v>
       </c>
       <c r="AA5" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6068</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>53805836</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>97632790</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NCB-2026-10-AFTERWORK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>After-Work Wind Down — Mua 02 tặng 01 bia khi mua kèm 01 snack (17:00–19:30)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TC_DAYPART</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>97</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5522</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.01757827230125902</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7523182</v>
+      </c>
+      <c r="S6" t="n">
+        <v>32500146</v>
+      </c>
+      <c r="T6" t="n">
+        <v>278389</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-632966</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.06430143894788738</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4329440</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>24014.84536082474</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>131</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2223220</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2329440</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NCB-2026-10-OFFICEEXCL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Office Exclusive — giảm 10% khách tòa văn phòng</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NCB_ET|NCB_MET|NCB_SKC</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TC_BASE</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>466</v>
+      </c>
+      <c r="O7" t="n">
+        <v>15482</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.03008070422713909</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>19355381</v>
+      </c>
+      <c r="S7" t="n">
+        <v>125422869</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1425986</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1144408</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.07964808706150228</v>
+      </c>
+      <c r="W7" t="n">
+        <v>17903587</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>765</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11148699</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>12903587</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NCB-2026-10-RESIDENTOFFICE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Resident / Office 10% (tiếp tục Q4)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NCB_ET|NCB_MET</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>TC_FREQ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>543</v>
+      </c>
+      <c r="O8" t="n">
+        <v>13399</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.04049662025289464</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>63178968</v>
+      </c>
+      <c r="S8" t="n">
+        <v>153524893</v>
+      </c>
+      <c r="T8" t="n">
+        <v>30073189</v>
+      </c>
+      <c r="U8" t="n">
+        <v>18043913</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.904000000000001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>15794742</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>853</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>27293314</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15794742</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NDC-2026-09-SETLUNCH199</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KHOA_MUON</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Set Lunch 199K (salad + main)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>TC_DAYPART</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2321</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3346</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.69375137652204</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>272364959</v>
+      </c>
+      <c r="S9" t="n">
+        <v>451051023</v>
+      </c>
+      <c r="T9" t="n">
+        <v>97069954</v>
+      </c>
+      <c r="U9" t="n">
+        <v>56241972</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.708699761487024</v>
+      </c>
+      <c r="W9" t="n">
+        <v>17003864</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5171.850064627316</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA9" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB9" t="n">
         <v>4783</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC9" t="n">
         <v>134595390</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD9" t="n">
         <v>12003864</v>
       </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
         <v>5000000</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-BIRTHDAY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Birthday Extra Value — tặng dessert + decor</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>TC_BASE</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>92</v>
+      </c>
+      <c r="O10" t="n">
+        <v>8591</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>54705936</v>
+      </c>
+      <c r="S10" t="n">
+        <v>196941370</v>
+      </c>
+      <c r="T10" t="n">
+        <v>22972295</v>
+      </c>
+      <c r="U10" t="n">
+        <v>13783377</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.347933727185328</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9784047</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>106348.3369565217</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>195</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>17190178</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>9784047</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-KHUNGSANG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Khung Sáng — Buy One, Share One + Morning Plate</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>TC_DAYPART</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1231</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4181</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2944867173485949</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>66296989</v>
+      </c>
+      <c r="S11" t="n">
+        <v>295824141</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8825540</v>
+      </c>
+      <c r="U11" t="n">
+        <v>95324</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1803229814567934</v>
+      </c>
+      <c r="W11" t="n">
+        <v>48942959</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10773.68887083672</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2648</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>25441200</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13262411</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22680547</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-PREBOOKPIZZA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pre-booking nhóm ≥3 tặng Pizza Kung Pao</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>TC_PARTY</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>833</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1932</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4312693483886144</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R12" t="n">
+        <v>105561501</v>
+      </c>
+      <c r="S12" t="n">
+        <v>760042810</v>
+      </c>
+      <c r="T12" t="n">
+        <v>14389873</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6633924</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2946883535781002</v>
+      </c>
+      <c r="W12" t="n">
+        <v>48830816</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>52618.02641056423</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>33156963</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>43830816</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NJFB-2026-10-RESIDENT15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Resident Privileges — giảm 15% F&amp;B cho cư dân (T7–CN)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>TC_FREQ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>SUA_CO_CHE</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>26</v>
+      </c>
+      <c r="O13" t="n">
+        <v>592</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.04390243902439025</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-2331414</v>
+      </c>
+      <c r="S13" t="n">
+        <v>42804757</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-3910724</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-2346434</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.5591348406634061</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6994241</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>63</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1579310</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>6994241</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NJFB-2026Q4-SETLUNCH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BAT_DAU</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Set Lunch — Mua 3 tặng 1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>TC_DAYPART</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>177</v>
+      </c>
+      <c r="O14" t="n">
+        <v>755</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2345868932383499</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>18558643</v>
+      </c>
+      <c r="S14" t="n">
+        <v>186711627</v>
+      </c>
+      <c r="T14" t="n">
+        <v>511590</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-693046</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.02271512963149984</v>
+      </c>
+      <c r="W14" t="n">
+        <v>22521980</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>446</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>13932452</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>20021980</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/05_plan_lock.xlsx
+++ b/data_input/05_plan_lock.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1061,7 +1061,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALL-2026-10-LOYALTY</t>
+          <t>NCB-2026-10-AFTERWORK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1071,37 +1071,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>After-Work Wind Down — Mua 02 tặng 01 bia Sapporo khi mua kèm 01 snack (17:00–19:30)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BAT_DAU</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NOIRE Loyalty (toàn hệ thống) — duy trì giảm 10% thành viên</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NCB_ET|NCB_MET|NCB_SKC|NDC_NTMK|NDC_BKL|NJFB_CRE|NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1111,64 +1116,64 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TC_FREQ</t>
+          <t>TC_DAYPART</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>CHAY_THU</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3336</v>
+        <v>45.21</v>
       </c>
       <c r="O5" t="n">
-        <v>34180</v>
+        <v>2913.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.01551713218063208</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="R5" t="n">
-        <v>65088526</v>
+        <v>3121931</v>
       </c>
       <c r="S5" t="n">
-        <v>1651946800</v>
+        <v>13486742</v>
       </c>
       <c r="T5" t="n">
-        <v>5294546</v>
+        <v>482286</v>
       </c>
       <c r="U5" t="n">
-        <v>3176728</v>
+        <v>289372</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05422917874905554</v>
+        <v>0.3870296836884847</v>
       </c>
       <c r="W5" t="n">
-        <v>97632790</v>
+        <v>1246122</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>27562.97279362973</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AA5" t="n">
         <v>0.092</v>
       </c>
       <c r="AB5" t="n">
-        <v>6068</v>
+        <v>60.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>53805836</v>
+        <v>1106304</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1246122</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1186,13 +1191,13 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97632790</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NCB-2026-10-AFTERWORK</t>
+          <t>NCB-2026-10-BLOOMINGVELVET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1202,17 +1207,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BAT_DAU</t>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>After-Work Wind Down — Mua 02 tặng 01 bia khi mua kèm 01 snack (17:00–19:30)</t>
+          <t>The Blooming Velvet 20/10 — tặng hoa 18–19/10, mang hoa đến 20/10 nhận 01 nước đặc biệt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1222,17 +1232,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NCB_MET</t>
+          <t>NCB_ET|NCB_MET|NCB_SKC</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1242,70 +1252,70 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>TC_DAYPART</t>
+          <t>TC_BASE</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CHAY_THU</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="O6" t="n">
-        <v>5522</v>
+        <v>832.01</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01757827230125902</v>
+        <v>0.09014287645918781</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="R6" t="n">
-        <v>7523182</v>
+        <v>5274145</v>
       </c>
       <c r="S6" t="n">
-        <v>32500146</v>
+        <v>22704924</v>
       </c>
       <c r="T6" t="n">
-        <v>278389</v>
+        <v>1530296</v>
       </c>
       <c r="U6" t="n">
-        <v>-632966</v>
+        <v>918177</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06430143894788738</v>
+        <v>0.5719882711210575</v>
       </c>
       <c r="W6" t="n">
-        <v>4329440</v>
+        <v>2675397</v>
       </c>
       <c r="X6" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>24014.84536082474</v>
+        <v>16000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="AA6" t="n">
         <v>0.092</v>
       </c>
       <c r="AB6" t="n">
-        <v>131</v>
+        <v>148.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2223220</v>
+        <v>2058628</v>
       </c>
       <c r="AD6" t="n">
-        <v>2329440</v>
+        <v>1200000</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1317,13 +1327,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1475397</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NCB-2026-10-OFFICEEXCL</t>
+          <t>NCB-2026-10-HALLOWEEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1333,17 +1343,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BAT_DAU</t>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Office Exclusive — giảm 10% khách tòa văn phòng</t>
+          <t>Halloween Night — 2 đồ uống LTO (Cranberry Spice Tea · Dark Cocoa Latte)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1358,76 +1373,73 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>TC_BASE</t>
+          <t>AOV_QTY</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CHAY_THU</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>466</v>
+        <v>174.86</v>
       </c>
       <c r="O7" t="n">
-        <v>15482</v>
+        <v>3529.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03008070422713909</v>
+        <v>0.04953891918691126</v>
       </c>
       <c r="Q7" t="n">
         <v>0.75</v>
       </c>
       <c r="R7" t="n">
-        <v>19355381</v>
+        <v>3826821</v>
       </c>
       <c r="S7" t="n">
-        <v>125422869</v>
+        <v>16531868</v>
       </c>
       <c r="T7" t="n">
-        <v>1425986</v>
+        <v>2603645</v>
       </c>
       <c r="U7" t="n">
-        <v>-1144408</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.07964808706150228</v>
+        <v>1562187</v>
       </c>
       <c r="W7" t="n">
-        <v>17903587</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="AA7" t="n">
         <v>0.092</v>
       </c>
       <c r="AB7" t="n">
-        <v>765</v>
+        <v>345.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>11148699</v>
+        <v>871109</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1436,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1448,13 +1460,13 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12903587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NCB-2026-10-RESIDENTOFFICE</t>
+          <t>NCB-2026-10-OFFICEEXCL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1464,37 +1476,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Office Exclusive — giảm 10% khách tòa văn phòng/dân cư (Empress Tower · Hallmark/The Mett · Galleria)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NCB_ET|NCB_MET</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BAT_DAU</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Resident / Office 10% (tiếp tục Q4)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>NCB_ET|NCB_MET</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1504,7 +1521,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>TC_FREQ</t>
+          <t>TC_BASE</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1513,34 +1530,34 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>543</v>
+        <v>236.67</v>
       </c>
       <c r="O8" t="n">
-        <v>13399</v>
+        <v>4632.84</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04049662025289464</v>
+        <v>0.05108596744395525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="R8" t="n">
-        <v>63178968</v>
+        <v>10394439</v>
       </c>
       <c r="S8" t="n">
-        <v>153524893</v>
+        <v>67355966</v>
       </c>
       <c r="T8" t="n">
-        <v>30073189</v>
+        <v>4131095</v>
       </c>
       <c r="U8" t="n">
-        <v>18043913</v>
+        <v>2478657</v>
       </c>
       <c r="V8" t="n">
-        <v>1.904000000000001</v>
+        <v>0.5961497644557124</v>
       </c>
       <c r="W8" t="n">
-        <v>15794742</v>
+        <v>6929626</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1549,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="AA8" t="n">
         <v>0.092</v>
       </c>
       <c r="AB8" t="n">
-        <v>853</v>
+        <v>508.58</v>
       </c>
       <c r="AC8" t="n">
-        <v>27293314</v>
+        <v>5307056</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1579,13 +1596,13 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15794742</v>
+        <v>6929626</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NDC-2026-09-SETLUNCH199</t>
+          <t>NCB-2026-10-RESIDENTOFFICE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1595,37 +1612,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KHOA_MUON</t>
+          <t>CEO_FINAL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Set Lunch 199K (salad + main)</t>
+          <t>Resident / Office 10% — đặc quyền thường xuyên (Extra Value, tiếp tục Q4)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_ET|NCB_MET</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1640,7 +1657,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>TC_DAYPART</t>
+          <t>TC_FREQ</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1649,61 +1666,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2321</v>
+        <v>542.62</v>
       </c>
       <c r="O9" t="n">
-        <v>3346</v>
+        <v>13749.07</v>
       </c>
       <c r="P9" t="n">
-        <v>0.69375137652204</v>
+        <v>0.03946593795944661</v>
       </c>
       <c r="Q9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>63550172</v>
+      </c>
+      <c r="S9" t="n">
+        <v>154426919</v>
+      </c>
+      <c r="T9" t="n">
+        <v>33368599</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20021160</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.100299528911425</v>
+      </c>
+      <c r="W9" t="n">
+        <v>15887543</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.3</v>
       </c>
-      <c r="R9" t="n">
-        <v>272364959</v>
-      </c>
-      <c r="S9" t="n">
-        <v>451051023</v>
-      </c>
-      <c r="T9" t="n">
-        <v>97069954</v>
-      </c>
-      <c r="U9" t="n">
-        <v>56241972</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.708699761487024</v>
-      </c>
-      <c r="W9" t="n">
-        <v>17003864</v>
-      </c>
-      <c r="X9" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5171.850064627316</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AA9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="AB9" t="n">
-        <v>4783</v>
+        <v>1166.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>134595390</v>
+        <v>24334957</v>
       </c>
       <c r="AD9" t="n">
-        <v>12003864</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1715,16 +1732,13 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
+        <v>15887543</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NDC-2026-10-BIRTHDAY</t>
+          <t>NCB-2026-11-VELVETEMERALD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1734,34 +1748,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>POSM &amp; Merchandise NCB Q4 — phần chưa gán cho chương trình</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NCB_ET|NCB_MET|NCB_SKC</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>BAT_DAU</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Birthday Extra Value — tặng dessert + decor</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>NDC_NTMK|NDC_BKL</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>2026-12-31</t>
@@ -1769,72 +1788,72 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>BRANDING</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>TC_BASE</t>
+          <t>BR_AWARE</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>DUYET</t>
+          <t>BRANDING</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>92</v>
+        <v>316</v>
       </c>
       <c r="O10" t="n">
-        <v>8591</v>
+        <v>23195.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0107</v>
+        <v>0.01362333211183204</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="R10" t="n">
-        <v>54705936</v>
+        <v>81466594</v>
       </c>
       <c r="S10" t="n">
-        <v>196941370</v>
+        <v>97759913</v>
       </c>
       <c r="T10" t="n">
-        <v>22972295</v>
+        <v>-2532576</v>
       </c>
       <c r="U10" t="n">
-        <v>13783377</v>
+        <v>-22182233</v>
       </c>
       <c r="V10" t="n">
-        <v>2.347933727185328</v>
+        <v>-0.0490270433739625</v>
       </c>
       <c r="W10" t="n">
-        <v>9784047</v>
+        <v>51656719</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>51656719</v>
       </c>
       <c r="Y10" t="n">
-        <v>106348.3369565217</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="AB10" t="n">
-        <v>195</v>
+        <v>623.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>17190178</v>
+        <v>24847525</v>
       </c>
       <c r="AD10" t="n">
-        <v>9784047</v>
+        <v>51656719</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>51656719</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1855,7 +1874,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NDC-2026-10-KHUNGSANG</t>
+          <t>NCB-2026-12-LIVEPERF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1865,115 +1884,115 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BAT_DAU</t>
+          <t>CEO_FINAL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Khung Sáng — Buy One, Share One + Morning Plate</t>
+          <t>Biểu diễn Violin/Saxophone Giáng sinh (SKC, 24–25/12)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NDC_NTMK</t>
+          <t>NCB_SKC</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>BRANDING</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>TC_DAYPART</t>
+          <t>BR_ENGAGE</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>CHAY_THU</t>
+          <t>BRANDING</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1231</v>
+        <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>4181</v>
+        <v>205.36</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2944867173485949</v>
+        <v>0.2434782608695653</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="R11" t="n">
-        <v>66296989</v>
+        <v>8316121</v>
       </c>
       <c r="S11" t="n">
-        <v>295824141</v>
+        <v>14969018</v>
       </c>
       <c r="T11" t="n">
-        <v>8825540</v>
+        <v>-4968443</v>
       </c>
       <c r="U11" t="n">
-        <v>95324</v>
+        <v>-6981066</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1803229814567934</v>
+        <v>-0.4968443035213598</v>
       </c>
       <c r="W11" t="n">
-        <v>48942959</v>
+        <v>10000000</v>
       </c>
       <c r="X11" t="n">
-        <v>13000000</v>
+        <v>10000000</v>
       </c>
       <c r="Y11" t="n">
-        <v>10773.68887083672</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="AB11" t="n">
-        <v>2648</v>
+        <v>85.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>25441200</v>
+        <v>2519481</v>
       </c>
       <c r="AD11" t="n">
-        <v>13262411</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>13000000</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -1982,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22680547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NDC-2026-10-PREBOOKPIZZA</t>
+          <t>NCB-2026-12-SECRETSANTA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2001,115 +2020,115 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BAT_DAU</t>
+          <t>CEO_FINAL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pre-booking nhóm ≥3 tặng Pizza Kung Pao</t>
+          <t>Secret Santa Envelope — HĐ ≥500K + ≥1 LTO Christmas rút quà từ Santa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NDC</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NDC_NTMK|NDC_BKL</t>
+          <t>NCB_ET|NCB_MET|NCB_SKC</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>TC_PARTY</t>
+          <t>AOV_VALUE</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>CHAY_THU</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>833</v>
+        <v>385.12</v>
       </c>
       <c r="O12" t="n">
-        <v>1932</v>
+        <v>8988.26</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4312693483886144</v>
+        <v>0.04284657019885836</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="R12" t="n">
-        <v>105561501</v>
+        <v>68183878</v>
       </c>
       <c r="S12" t="n">
-        <v>760042810</v>
+        <v>245461960</v>
       </c>
       <c r="T12" t="n">
-        <v>14389873</v>
+        <v>32771418</v>
       </c>
       <c r="U12" t="n">
-        <v>6633924</v>
+        <v>19662851</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2946883535781002</v>
+        <v>3.92788129451844</v>
       </c>
       <c r="W12" t="n">
-        <v>48830816</v>
+        <v>8343281</v>
       </c>
       <c r="X12" t="n">
-        <v>5000000</v>
+        <v>8343281</v>
       </c>
       <c r="Y12" t="n">
-        <v>52618.02641056423</v>
+        <v>21664.1072912339</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="AB12" t="n">
-        <v>2500</v>
+        <v>760.0599999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>33156963</v>
+        <v>20796261</v>
       </c>
       <c r="AD12" t="n">
-        <v>43830816</v>
+        <v>8343281</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2127,7 +2146,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NJFB-2026-10-RESIDENT15</t>
+          <t>NCB-2026-12-XMASMENU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2137,32 +2156,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BAT_DAU</t>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Resident Privileges — giảm 15% F&amp;B cho cư dân (T7–CN)</t>
+          <t>Seasonal Menu Christmas — LTO drinks &amp; cake (+ set 2 người)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NJFB</t>
+          <t>NCB</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NJFB_CRE|NJFB_SSV</t>
+          <t>NCB_ET|NCB_MET|NCB_SKC</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2172,48 +2196,45 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>TC</t>
+          <t>AOV</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>TC_FREQ</t>
+          <t>AOV_VALUE</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SUA_CO_CHE</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>195.82</v>
       </c>
       <c r="O13" t="n">
-        <v>592</v>
+        <v>8988.26</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04390243902439025</v>
+        <v>0.02178665607347895</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="R13" t="n">
-        <v>-2331414</v>
+        <v>5142745</v>
       </c>
       <c r="S13" t="n">
-        <v>42804757</v>
+        <v>18513881</v>
       </c>
       <c r="T13" t="n">
-        <v>-3910724</v>
+        <v>3498956</v>
       </c>
       <c r="U13" t="n">
-        <v>-2346434</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.5591348406634061</v>
+        <v>2099374</v>
       </c>
       <c r="W13" t="n">
-        <v>6994241</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2222,16 +2243,16 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="AB13" t="n">
-        <v>63</v>
+        <v>386.47</v>
       </c>
       <c r="AC13" t="n">
-        <v>1579310</v>
+        <v>1170656</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2252,13 +2273,13 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>6994241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NJFB-2026Q4-SETLUNCH</t>
+          <t>NDC-2026-09-SETLUNCH199</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2268,42 +2289,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BAT_DAU</t>
+          <t>CEO_FINAL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Set Lunch — Mua 3 tặng 1</t>
+          <t>Set Lunch 199K (salad + main)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NJFB</t>
+          <t>NDC</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NJFB_CRE|NJFB_SSV</t>
+          <t>NDC_NTMK</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2318,65 +2339,65 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CHAY_THU</t>
+          <t>DUYET</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>177</v>
+        <v>723.6799999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>755</v>
+        <v>3419.58</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2345868932383499</v>
+        <v>0.2116283937696238</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="R14" t="n">
-        <v>18558643</v>
+        <v>116700839</v>
       </c>
       <c r="S14" t="n">
-        <v>186711627</v>
+        <v>160952948</v>
       </c>
       <c r="T14" t="n">
-        <v>511590</v>
+        <v>64404525</v>
       </c>
       <c r="U14" t="n">
-        <v>-693046</v>
+        <v>36642715</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02271512963149984</v>
+        <v>7.36660879211881</v>
       </c>
       <c r="W14" t="n">
-        <v>22521980</v>
+        <v>8742764</v>
       </c>
       <c r="X14" t="n">
-        <v>2500000</v>
+        <v>5000000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>5171.849436214902</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="AA14" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>446</v>
+        <v>1484.86</v>
       </c>
       <c r="AC14" t="n">
-        <v>13932452</v>
+        <v>33400577</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3742764</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2500000</v>
+        <v>5000000</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2388,7 +2409,2854 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20021980</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-BIRTHDAY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Birthday Extra Value — tặng dessert + decor</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>TC_BASE</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8474.93</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>53935505</v>
+      </c>
+      <c r="S15" t="n">
+        <v>194167818</v>
+      </c>
+      <c r="T15" t="n">
+        <v>23146381</v>
+      </c>
+      <c r="U15" t="n">
+        <v>13887828</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.398050931158904</v>
+      </c>
+      <c r="W15" t="n">
+        <v>9652164</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>106442.0379355977</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>192.48</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>16444571</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>9652164</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dessert Halloween (LTO)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AOV_QTY</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>921.1900000000001</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.05617746462254213</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2036778</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8798883</v>
+      </c>
+      <c r="T16" t="n">
+        <v>273083</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-236150</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2730830459458958</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>109.84</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>586496</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-HERWONDERS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Her Wonders 20/10 — tặng hoa 18–19/10, mang hoa đến 20/10 nhận 01 mocktail</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>TC_BASE</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>28</v>
+      </c>
+      <c r="O17" t="n">
+        <v>810.65</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.03454038228878303</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5732496</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20636987</v>
+      </c>
+      <c r="T17" t="n">
+        <v>486370</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-508178</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1621448581282512</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2999600</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>35700</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1747799</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>999600</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-KHUNGSANG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Khung Sáng — Buy One, Share One + Morning Plate</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>TC_DAYPART</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>883.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3105.54</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.2844283474960811</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>47529861</v>
+      </c>
+      <c r="S18" t="n">
+        <v>212083241</v>
+      </c>
+      <c r="T18" t="n">
+        <v>11629129</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5377478</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3905727581021707</v>
+      </c>
+      <c r="W18" t="n">
+        <v>29774553</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10771.35514547719</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1878.23</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>18251296</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>9514338</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>16260215</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NDC-2026-10-PREBOOKPIZZA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pre-booking nhóm ≥3 tặng Pizza Kung Pao / Salad Burrata</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>TC_PARTY</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>72.34999999999999</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1886.57</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.03835142161607535</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4595552405422167</v>
+      </c>
+      <c r="R19" t="n">
+        <v>34783907</v>
+      </c>
+      <c r="S19" t="n">
+        <v>69510564</v>
+      </c>
+      <c r="T19" t="n">
+        <v>12363448</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5418069</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.404053174432377</v>
+      </c>
+      <c r="W19" t="n">
+        <v>8805541</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>52599.04630269523</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>217.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10588717</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3805541</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NDC-2026-11-WINTERBRAND</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>POSM &amp; Merchandise NDC Q4 — phần chưa gán cho chương trình</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>BR_AWARE</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>180</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8474.93</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.02123911705956224</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R20" t="n">
+        <v>104413326</v>
+      </c>
+      <c r="S20" t="n">
+        <v>132666343</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3949399</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-21448380</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.06632624416533511</v>
+      </c>
+      <c r="W20" t="n">
+        <v>59545049</v>
+      </c>
+      <c r="X20" t="n">
+        <v>59545049</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>31834918</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>59545049</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>59545049</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NDC-2026-11-WINTERNIGHTS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NOIRE Winter Nights — key window: Winter LTO (main, dessert)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>AOV_VALUE</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>28.45</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4449.34</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.006394572878147771</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4854130</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20969841</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2951829</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1771098</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1479991</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NDC-2026-12-FESTIVALMERCH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Festival Merch Collection — bill ≥800K rút Santa Box</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AOV_VALUE</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>21</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3284.03</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.006394572878147771</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5289720</v>
+      </c>
+      <c r="S22" t="n">
+        <v>22851592</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2761764</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1657058</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.07046314343169</v>
+      </c>
+      <c r="W22" t="n">
+        <v>454951</v>
+      </c>
+      <c r="X22" t="n">
+        <v>454951</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>21664.33333333333</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1612800</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>454951</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NDC-2026-12-XMASSET</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Christmas Eve — set 5 courses 690K/khách (24–25/12)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NDC_NTMK|NDC_BKL</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AOV_PRICE</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>184.24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.6616456944432739</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>60844008</v>
+      </c>
+      <c r="S23" t="n">
+        <v>132450078</v>
+      </c>
+      <c r="T23" t="n">
+        <v>17647822</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4588693</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.9119459079251876</v>
+      </c>
+      <c r="W23" t="n">
+        <v>19351830</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>35700</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>18550927</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4351830</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NJFB-2026-10-GSKAIDAN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Guest Shift #1 KAIDAN — Chuyện Kể Nửa Đêm (Halloween)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BR_AWARE</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.5616850551654965</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4737437</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10232865</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2150280</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1050168</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.583800552235572</v>
+      </c>
+      <c r="W24" t="n">
+        <v>600000</v>
+      </c>
+      <c r="X24" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NJFB-2026-10-HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Halloween Night — The Crest, vé 500K/khách</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AOV_VALUE</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.8776328986960883</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>21055277</v>
+      </c>
+      <c r="S25" t="n">
+        <v>45479399</v>
+      </c>
+      <c r="T25" t="n">
+        <v>12423468</v>
+      </c>
+      <c r="U25" t="n">
+        <v>7454081</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NJFB-2026-10-RESIDENT15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Resident Privileges — giảm 15% F&amp;B cho cư dân (T7–CN)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>TC_FREQ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>26</v>
+      </c>
+      <c r="O26" t="n">
+        <v>599.62</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.04336043360433604</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6809186</v>
+      </c>
+      <c r="S26" t="n">
+        <v>41672221</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1679592</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1007755</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2466656298750682</v>
+      </c>
+      <c r="W26" t="n">
+        <v>6809186</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>63.34</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4537195</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>6809186</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NJFB-2026-10-SWEETBLOOM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sweet Bloom 20/10 — tặng wagashi/nerikiri</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>TC_BASE</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>148.98</v>
+      </c>
+      <c r="O27" t="n">
+        <v>202.29</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.7364830508474576</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>71606763</v>
+      </c>
+      <c r="S27" t="n">
+        <v>309341215</v>
+      </c>
+      <c r="T27" t="n">
+        <v>29841607</v>
+      </c>
+      <c r="U27" t="n">
+        <v>15904964</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.549671242031451</v>
+      </c>
+      <c r="W27" t="n">
+        <v>11704100</v>
+      </c>
+      <c r="X27" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>297.96</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>23831267</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>6704100</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NJFB-2026-10-WEEKLYOFFER</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Weekly Offer (T2–T3 sushi roll −10% · T5 nhóm ≥3 tặng Carbonara Udon · CN pre-book tặng dessert)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>TC_PARTY</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>418.07</v>
+      </c>
+      <c r="O28" t="n">
+        <v>733</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.5703547066848568</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>154480552</v>
+      </c>
+      <c r="S28" t="n">
+        <v>876846228</v>
+      </c>
+      <c r="T28" t="n">
+        <v>71385244</v>
+      </c>
+      <c r="U28" t="n">
+        <v>38831146</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.854368928952293</v>
+      </c>
+      <c r="W28" t="n">
+        <v>25009116</v>
+      </c>
+      <c r="X28" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>12285.36369507499</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1128.32</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>54519358</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>5136142</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>9872974</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NJFB-2026-11-GSYUKIAKARI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Guest Shift #2 YUKIAKARI</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>BR_AWARE</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.5616850551654965</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4737437</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10232865</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2150280</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1050168</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.583800552235572</v>
+      </c>
+      <c r="W29" t="n">
+        <v>600000</v>
+      </c>
+      <c r="X29" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NJFB-2026-11-LIGHTSBRAND</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>POSM &amp; Merchandise NJFB Q4 — phần chưa gán cho chương trình</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>BR_AWARE</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>120</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2326.29</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.05158437730287399</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>177799505</v>
+      </c>
+      <c r="S30" t="n">
+        <v>240029332</v>
+      </c>
+      <c r="T30" t="n">
+        <v>55261241</v>
+      </c>
+      <c r="U30" t="n">
+        <v>13998065</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.153758860447747</v>
+      </c>
+      <c r="W30" t="n">
+        <v>47896699</v>
+      </c>
+      <c r="X30" t="n">
+        <v>47896699</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>303.98</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>59173008</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>47896699</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>47896699</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NJFB-2026-11-NIGHTOFLIGHTS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Night of Lights &amp; Flavors — key window: 5 LTO à la carte + HĐ ≥1.000K rút quà (tháng 12)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AOV_VALUE</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1221.3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.0269939752194251</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>15264709</v>
+      </c>
+      <c r="S31" t="n">
+        <v>65943542</v>
+      </c>
+      <c r="T31" t="n">
+        <v>8553169</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5131901</v>
+      </c>
+      <c r="V31" t="n">
+        <v>28.20029433153406</v>
+      </c>
+      <c r="W31" t="n">
+        <v>303301</v>
+      </c>
+      <c r="X31" t="n">
+        <v>303301</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9199.302396117682</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>83.51000000000001</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5080209</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>303301</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NJFB-2026-11-SETHOKKAIDO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NIGHT OF LIGHTS &amp; FLAVORS — Set đôi Hokkaido 1.499K/2 · Set Hội Ngộ 2.190K/4</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AOV_PRICE</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>150.72</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1221.3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.1234094816998281</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="R32" t="n">
+        <v>46916573</v>
+      </c>
+      <c r="S32" t="n">
+        <v>281652569</v>
+      </c>
+      <c r="T32" t="n">
+        <v>27220644</v>
+      </c>
+      <c r="U32" t="n">
+        <v>16332387</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>422.02</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>15614187</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NJFB-2026-12-GSOMOIDE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Guest Shift #3 OMOIDE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>BR_AWARE</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>BRANDING</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.5616850551654965</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4737437</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10232865</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2150280</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1050168</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3.583800552235572</v>
+      </c>
+      <c r="W33" t="n">
+        <v>600000</v>
+      </c>
+      <c r="X33" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NJFB-2026-12-XMASSUSHITREE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Xmas Pre-booking — nhóm 4 tặng Sushi Tree</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>TC_PARTY</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>DUYET</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>180</v>
+      </c>
+      <c r="O34" t="n">
+        <v>901.4400000000001</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.1996814605272541</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>105281893</v>
+      </c>
+      <c r="S34" t="n">
+        <v>568522220</v>
+      </c>
+      <c r="T34" t="n">
+        <v>17783765</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6670259</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.410710511803242</v>
+      </c>
+      <c r="W34" t="n">
+        <v>43300000</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>185000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>720</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>35038603</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>33300000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NJFB-2026Q4-SETLUNCH</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CEO_FINAL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Set Lunch — Mua 3 tặng 1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NJFB_CRE|NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>TC_DAYPART</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>CHAY_THU</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>51</v>
+      </c>
+      <c r="O35" t="n">
+        <v>783.86</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.06506287588846364</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.6061475409836066</v>
+      </c>
+      <c r="R35" t="n">
+        <v>16408944</v>
+      </c>
+      <c r="S35" t="n">
+        <v>44995681</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1231488</v>
+      </c>
+      <c r="U35" t="n">
+        <v>-1261107</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.1381679957396817</v>
+      </c>
+      <c r="W35" t="n">
+        <v>8912975</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>76725</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4836903</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3912975</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
